--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationquantity.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationquantity.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Quantity</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Quantity|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -466,7 +466,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUnitMERIT9_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUnitMERIT9_VS|1.1.0a</t>
   </si>
   <si>
     <t>PQ.code, MO.currency, PQ.translation.code</t>
@@ -801,7 +801,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="57.328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="49.63671875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="55.12890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationquantity.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationquantity.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Quantity|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Quantity</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -466,7 +466,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUnitMERIT9_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationUnitMERIT9_VS</t>
   </si>
   <si>
     <t>PQ.code, MO.currency, PQ.translation.code</t>
@@ -801,7 +801,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="57.328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="55.12890625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="49.63671875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
